--- a/code/Excel/tim.xlsx
+++ b/code/Excel/tim.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,26 +422,6 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>!</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -449,26 +429,6 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>!</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -771,7 +731,470 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/code/Excel/tim.xlsx
+++ b/code/Excel/tim.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-16320" yWindow="-2445" windowWidth="16440" windowHeight="29040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -46,11 +45,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,21 +441,6 @@
           <t>B3</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>!</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,21 +453,6 @@
           <t>B4</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>!</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -495,14 +465,14 @@
           <t>B5</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>D5</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>D3</t>
         </is>
       </c>
     </row>
@@ -517,129 +487,104 @@
           <t>B6</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>D6</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D4</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A7</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>B7</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>C7</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>D7</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>D5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>D8</t>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>D6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B9</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>D9</t>
+          <t>B8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>D10</t>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>D7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Is</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Great</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Always</t>
+          <t>B10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>!</t>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>D8</t>
         </is>
       </c>
     </row>
@@ -666,7 +611,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>!</t>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>D9</t>
         </is>
       </c>
     </row>
@@ -693,7 +643,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>!</t>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>D10</t>
         </is>
       </c>
     </row>
@@ -727,34 +682,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>end</t>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>!</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tim</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Is</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Great</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>!</t>
+          <t>end</t>
         </is>
       </c>
     </row>
@@ -842,34 +797,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>end</t>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>!</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tim</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Is</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Great</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>!</t>
+          <t>end</t>
         </is>
       </c>
     </row>
@@ -957,34 +912,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>end</t>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>!</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tim</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Is</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Great</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>!</t>
+          <t>end</t>
         </is>
       </c>
     </row>
@@ -1072,34 +1027,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>end</t>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>!</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tim</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Is</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Great</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>!</t>
+          <t>end</t>
         </is>
       </c>
     </row>
@@ -1186,6 +1141,33 @@
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>end</t>
         </is>
